--- a/artfynd/A 12950-2026 artfynd.xlsx
+++ b/artfynd/A 12950-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137144218</v>
       </c>
       <c r="B2" t="n">
-        <v>56572</v>
+        <v>56585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12950-2026 artfynd.xlsx
+++ b/artfynd/A 12950-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137144218</v>
       </c>
       <c r="B2" t="n">
-        <v>56585</v>
+        <v>56587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12950-2026 artfynd.xlsx
+++ b/artfynd/A 12950-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137144218</v>
       </c>
       <c r="B2" t="n">
-        <v>56587</v>
+        <v>56597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12950-2026 artfynd.xlsx
+++ b/artfynd/A 12950-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137144218</v>
       </c>
       <c r="B2" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12950-2026 artfynd.xlsx
+++ b/artfynd/A 12950-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137144218</v>
       </c>
       <c r="B2" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
